--- a/docs/ops/SCALABILITY_REVIEW_WORKBOOK.xlsx
+++ b/docs/ops/SCALABILITY_REVIEW_WORKBOOK.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence &amp; Cases" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Risks" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement Waves" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave Gates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Tracking" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -507,6 +509,30 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>Eerst stabiliseren, dan systemiseren, pas daarna lichte automation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fix program source</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>docs/active/SCALABILITY_FIX_PROGRAM_PLAN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Operating model</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hybride: CRM primair voor leads, app primair voor delivery, scorecard als reviewmirror.</t>
         </is>
       </c>
     </row>
@@ -839,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -875,6 +901,16 @@
           <t>Follow-up</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fix-program step</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Evidence status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -902,6 +938,16 @@
           <t>Maak live pipeline verplicht werkritme.</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Nog niet bewezen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -929,6 +975,16 @@
           <t>Verbind lijst direct met actieve pipeline.</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Seed-list aanwezig</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -956,6 +1012,16 @@
           <t>Wekelijks vullen en reviewen.</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nog niet bewezen</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -983,6 +1049,16 @@
           <t>Voeg live checkpointoverzicht toe.</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nog niet bewezen</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1010,6 +1086,16 @@
           <t>Vertaal naar live operationsboard.</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Design aanwezig</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1035,6 +1121,16 @@
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Na elke maandreview actualiseren.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vroege start</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1457,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Live pipeline, actieve scorecard, maandreview, deliveryoverzicht, ingevulde capacity map.</t>
+          <t>Live pipeline, actieve scorecard, maandreview, deliveryoverzicht, ingevulde capacity map, source-of-truth charter, hybride werklaag hard gemaakt.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1388,7 +1484,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Defectlog, rolling metrics, delegated run, proof checkpoints.</t>
+          <t>Defectlog, rolling metrics, delegated run, proof checkpoints, ownergrenzen.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1415,7 +1511,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Automation shortlist met businesscase, duidelijke ops-/foundergrenzen.</t>
+          <t>Automation shortlist met businesscase, duidelijke ops-/foundergrenzen, 2x volume boundary test.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1426,6 +1522,304 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Dag 90</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Wave</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Gate evidence</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Primary systems</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Live pipeline, scorecard rhythm, delivery visibility, capacity map, source-of-truth charter</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CRM + app + scorecard + monthly review</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Go/no-go pas na eerste echte maandreview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rolling metrics, role clarity, proof capture, delegated run</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Scorecard + workbook + learning + decision log</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Blocked by Wave 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Start alleen na bewezen ritme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Friction shortlist, automation business case, 2x volume boundary test</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Workbook + monthly review + decision log</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Blocked by Wave 2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Start alleen na metrics en delegated run.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bottleneck</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Fix-program step</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Owner type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Evidence status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pipeline-instrumentatie leeg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Nog niet bewezen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Weekly cadence nog niet bewezen</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nog niet bewezen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Monthly governance te licht</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nog niet bewezen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Founder als centrale triage</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wave 2 - Step 2.3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Founder + future operator</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nog open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Deliverycheckpoints niet centraal zichtbaar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wave 1 - Step 1.3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ops / delivery owner</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Repo-laag bestaat; ritme nog niet bewezen</t>
         </is>
       </c>
     </row>
